--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -6,6 +6,7 @@
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
     <sheet name="Staff" sheetId="2" r:id="rId2"/>
     <sheet name="Ticket" sheetId="3" r:id="rId3"/>
+    <sheet name="ServiceReport" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -551,7 +552,7 @@
         <v/>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>78787888</v>
       </c>
     </row>
     <row r="10">
@@ -1026,4 +1027,14 @@
     <ignoredError numberStoredAsText="1" sqref="A1:O7"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetData/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -552,7 +552,7 @@
         <v/>
       </c>
       <c r="E9">
-        <v>78787888</v>
+        <v>78787953</v>
       </c>
     </row>
     <row r="10">

--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -589,9 +589,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>C-0000000000007</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>the@gaming.thing</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>C-0000000000008</v>
+      </c>
+      <c r="B13" t="str">
+        <v>new name test!!!</v>
+      </c>
+      <c r="C13" t="str">
+        <v>the@gaming.test</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -7,6 +7,8 @@
     <sheet name="Staff" sheetId="2" r:id="rId2"/>
     <sheet name="Ticket" sheetId="3" r:id="rId3"/>
     <sheet name="ServiceReport" sheetId="4" r:id="rId4"/>
+    <sheet name="StaffRoster" sheetId="5" r:id="rId5"/>
+    <sheet name="Appointment" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,9 +415,6 @@
         <v>Email</v>
       </c>
       <c r="D1" t="str">
-        <v>Password</v>
-      </c>
-      <c r="E1" t="str">
         <v>Credits</v>
       </c>
     </row>
@@ -429,10 +428,7 @@
       <c r="C2" t="str">
         <v>w@gmail.com</v>
       </c>
-      <c r="D2" t="str">
-        <v>w</v>
-      </c>
-      <c r="E2">
+      <c r="D2">
         <v>9997.5</v>
       </c>
     </row>
@@ -446,10 +442,7 @@
       <c r="C3" t="str">
         <v>hh@123.com</v>
       </c>
-      <c r="D3" t="str">
-        <v>12</v>
-      </c>
-      <c r="E3">
+      <c r="D3">
         <v>2</v>
       </c>
     </row>
@@ -463,10 +456,7 @@
       <c r="C4" t="str">
         <v>hi@gmail.com</v>
       </c>
-      <c r="D4" t="str">
-        <v>hi</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
         <v>2</v>
       </c>
     </row>
@@ -480,10 +470,7 @@
       <c r="C5" t="str">
         <v>debug@example.com</v>
       </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5">
+      <c r="D5">
         <v>0</v>
       </c>
     </row>
@@ -497,10 +484,7 @@
       <c r="C6" t="str">
         <v>fresh-user-1789968450253@example.com</v>
       </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6">
+      <c r="D6">
         <v>0</v>
       </c>
     </row>
@@ -514,10 +498,7 @@
       <c r="C7" t="str">
         <v>dorothy@600gmail.com</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7">
+      <c r="D7">
         <v>0</v>
       </c>
     </row>
@@ -531,10 +512,7 @@
       <c r="C8" t="str">
         <v>tom@gmail.com</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
+      <c r="D8">
         <v>0</v>
       </c>
     </row>
@@ -548,10 +526,7 @@
       <c r="C9" t="str">
         <v>ya@rawr.waow</v>
       </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
+      <c r="D9">
         <v>78787953</v>
       </c>
     </row>
@@ -565,10 +540,7 @@
       <c r="C10" t="str">
         <v>test-verify-1789968157434@example.com</v>
       </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
+      <c r="D10">
         <v>0</v>
       </c>
     </row>
@@ -582,10 +554,7 @@
       <c r="C11" t="str">
         <v>ya@rar.waow</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11">
+      <c r="D11">
         <v>0</v>
       </c>
     </row>
@@ -594,15 +563,12 @@
         <v>C-0000000000007</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>the game</v>
       </c>
       <c r="C12" t="str">
         <v>the@gaming.thing</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
+      <c r="D12">
         <v>0</v>
       </c>
     </row>
@@ -616,16 +582,70 @@
       <c r="C13" t="str">
         <v>the@gaming.test</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13">
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>C-0000000000009</v>
+      </c>
+      <c r="B14" t="str">
+        <v>the new name test 2 boogaloo</v>
+      </c>
+      <c r="C14" t="str">
+        <v>oh@my.goodness</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>C-0000000000010</v>
+      </c>
+      <c r="B15" t="str">
+        <v>whalter whiet</v>
+      </c>
+      <c r="C15" t="str">
+        <v>the@gaming.TWO</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>C-0000000000011</v>
+      </c>
+      <c r="B16" t="str">
+        <v>help me please</v>
+      </c>
+      <c r="C16" t="str">
+        <v>help@me.please</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>C-0000000000012</v>
+      </c>
+      <c r="B17" t="str">
+        <v>the tenth one</v>
+      </c>
+      <c r="C17" t="str">
+        <v>the@tenth.one</v>
+      </c>
+      <c r="D17">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -725,22 +745,16 @@
         <v>ya@rar.waow</v>
       </c>
       <c r="D5" t="str">
-        <v>madness</v>
+        <v>scrypt:006ae7d8472b684b0f5d4dbc97b3f0f0:0ba23311a3bc929055cf9c5cd00ca67d160f3598b0442605c2b4dfaf6a4807a90b76c00d90ba9a72104894757303c94a2e33d14295cdacd1ee61dc190273cffd</v>
       </c>
       <c r="E5" t="str">
         <v>IT Support Technician</v>
       </c>
       <c r="F5" t="str">
-        <v>TBA</v>
+        <v>Information Technology</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1"/>
-    <hyperlink ref="C4" r:id="rId2"/>
-    <hyperlink ref="C5" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
@@ -749,7 +763,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:W11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -797,6 +811,30 @@
       <c r="O1" t="str">
         <v>On-site Support Type</v>
       </c>
+      <c r="P1" t="str">
+        <v>Assigned Staff ID</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Appointment Address</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Visit Technician</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Project Estimated Hours</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Credits Charged</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Billable Credits</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Unpaid Credits</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Credit Settlement Status</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1035,13 +1073,13 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-30</v>
       </c>
       <c r="J7" t="str">
-        <v>03:00</v>
+        <v>03:35</v>
       </c>
       <c r="K7" t="str">
-        <v>Pending</v>
+        <v>Reschedule Required</v>
       </c>
       <c r="L7" t="str">
         <v>2026-09-21T09:56:10.988Z</v>
@@ -1050,15 +1088,285 @@
         <v/>
       </c>
       <c r="N7">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O7" t="str">
         <v>Project</v>
       </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>gredfwrwd</v>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>T-1791360278642</v>
+      </c>
+      <c r="B8" t="str">
+        <v>C-0000000000004</v>
+      </c>
+      <c r="C8" t="str">
+        <v>josiah wimbleton</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ya@rawr.waow</v>
+      </c>
+      <c r="E8" t="str">
+        <v>completet this!!!!</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Remote Support</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Closed</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Miguel</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L8" t="str">
+        <v>2026-10-07T08:04:38.642Z</v>
+      </c>
+      <c r="M8" t="str">
+        <v>done</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>R-f29820c4-b6e1-4282-8818-b8e5eff883ae</v>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8" t="str">
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>T-1791360705516</v>
+      </c>
+      <c r="B9" t="str">
+        <v>C-0000000000004</v>
+      </c>
+      <c r="C9" t="str">
+        <v>josiah wimbleton</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ya@rawr.waow</v>
+      </c>
+      <c r="E9" t="str">
+        <v>MAKE THIS PENDING!!!!!</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Remote Support</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Miguel</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-10-07T08:11:45.516Z</v>
+      </c>
+      <c r="M9" t="str">
+        <v>pay me</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>R-f29820c4-b6e1-4282-8818-b8e5eff883ae</v>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>T-1791516077968</v>
+      </c>
+      <c r="B10" t="str">
+        <v>C-0000000000011</v>
+      </c>
+      <c r="C10" t="str">
+        <v>help me please</v>
+      </c>
+      <c r="D10" t="str">
+        <v>help@me.please</v>
+      </c>
+      <c r="E10" t="str">
+        <v>help me please</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Remote Support</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="H10" t="str">
+        <v>josiah wimbleton</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2026-10-09T03:21:17.968Z</v>
+      </c>
+      <c r="M10" t="str">
+        <v>pay up</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v>S-004</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>T-1791784361878</v>
+      </c>
+      <c r="B11" t="str">
+        <v>C-0000000000012</v>
+      </c>
+      <c r="C11" t="str">
+        <v>the tenth one</v>
+      </c>
+      <c r="D11" t="str">
+        <v>the@tenth.one</v>
+      </c>
+      <c r="E11" t="str">
+        <v>the 10th one</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Phone Support</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Closed</v>
+      </c>
+      <c r="H11" t="str">
+        <v>josiah wimbleton</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L11" t="str">
+        <v>2026-10-12T05:52:41.878Z</v>
+      </c>
+      <c r="M11" t="str">
+        <v>the 10th one</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v>S-004</v>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11" t="str">
+        <v>Not Applicable</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1067,8 +1375,313 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Staff ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Role</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Department</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Active</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Login Staff ID</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>S-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="C2" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="E2" t="str">
+        <v>itadmin@company.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H2" t="str">
+        <v>S-001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>S-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>John</v>
+      </c>
+      <c r="C3" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="E3" t="str">
+        <v>john@gmail.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H3" t="str">
+        <v>S-002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>S-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Taro</v>
+      </c>
+      <c r="C4" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="E4" t="str">
+        <v>taro@gmail.com</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H4" t="str">
+        <v>S-003</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>S-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>josiah wimbleton</v>
+      </c>
+      <c r="C5" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="E5" t="str">
+        <v>ya@rar.waow</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H5" t="str">
+        <v>S-004</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>R-f29820c4-b6e1-4282-8818-b8e5eff883ae</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Miguel</v>
+      </c>
+      <c r="C6" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="E6" t="str">
+        <v>miguel@innocom.com.sg</v>
+      </c>
+      <c r="F6" t="str">
+        <v>85690679</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Appointment ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Ticket ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Staff ID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Start Time</v>
+      </c>
+      <c r="F1" t="str">
+        <v>End Date</v>
+      </c>
+      <c r="G1" t="str">
+        <v>End Time</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Actual Start Date</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Actual Start Time</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Actual End Date</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Actual End Time</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Project Days</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Project Day Mode</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Service Sessions</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Project Complete</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Address</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Scheduling Note</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Service Report ID</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Created At</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A-3e099769-ab4e-41b7-82b4-c6eaa57f586f</v>
+      </c>
+      <c r="B2" t="str">
+        <v>T-1791364084704</v>
+      </c>
+      <c r="C2" t="str">
+        <v>S-004</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-10-08</v>
+      </c>
+      <c r="E2" t="str">
+        <v>18:08</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-10-08</v>
+      </c>
+      <c r="G2" t="str">
+        <v>19:08</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>[]</v>
+      </c>
+      <c r="O2" t="str">
+        <v>No</v>
+      </c>
+      <c r="P2" t="str">
+        <v>hi</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v>2026-10-07T09:08:04.731Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:T2"/>
+  </ignoredErrors>
+</worksheet>
 </file>